--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.102</v>
+        <v>0.1395</v>
       </c>
       <c r="E2">
-        <v>0.18395</v>
+        <v>-0.332</v>
       </c>
       <c r="G2">
-        <v>0.1226211604095563</v>
+        <v>-0.03230198902117346</v>
       </c>
       <c r="H2">
-        <v>0.1226211604095563</v>
+        <v>-0.03230198902117346</v>
       </c>
       <c r="I2">
-        <v>-0.07804095563139932</v>
+        <v>0.05173593783417695</v>
       </c>
       <c r="J2">
-        <v>-0.07774734462057235</v>
+        <v>0.04623650618043326</v>
       </c>
       <c r="K2">
-        <v>4.198</v>
+        <v>9.661999999999999</v>
       </c>
       <c r="L2">
-        <v>0.02865529010238908</v>
+        <v>0.06888144293148928</v>
       </c>
       <c r="M2">
-        <v>0.918</v>
+        <v>2.145</v>
       </c>
       <c r="N2">
-        <v>0.009654011988642339</v>
+        <v>0.03463028737487892</v>
       </c>
       <c r="O2">
-        <v>0.2186755597903764</v>
+        <v>0.2220037259366591</v>
       </c>
       <c r="P2">
-        <v>0.893</v>
+        <v>2.125</v>
       </c>
       <c r="Q2">
-        <v>0.009391103165422231</v>
+        <v>0.03430739425250242</v>
       </c>
       <c r="R2">
-        <v>0.212720343020486</v>
+        <v>0.2199337611260609</v>
       </c>
       <c r="S2">
-        <v>0.025</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="T2">
-        <v>0.02723311546840959</v>
+        <v>0.009324009324009333</v>
       </c>
       <c r="U2">
-        <v>117.491</v>
+        <v>87.917</v>
       </c>
       <c r="V2">
-        <v>1.235576821958145</v>
+        <v>1.419389731998709</v>
       </c>
       <c r="W2">
-        <v>-0.01912225705329154</v>
+        <v>0.03845203753077786</v>
       </c>
       <c r="X2">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="Y2">
-        <v>-0.1020109895237249</v>
+        <v>-0.1051939080448581</v>
       </c>
       <c r="Z2">
-        <v>1.071141332163486</v>
+        <v>2.048664359053002</v>
       </c>
       <c r="AA2">
-        <v>-0.06616541353383458</v>
+        <v>-0.02975815090106463</v>
       </c>
       <c r="AB2">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="AC2">
-        <v>-0.149054146004268</v>
+        <v>-0.1734040964767006</v>
       </c>
       <c r="AD2">
-        <v>11.587</v>
+        <v>6.168</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.587</v>
+        <v>6.168</v>
       </c>
       <c r="AG2">
-        <v>-105.904</v>
+        <v>-81.749</v>
       </c>
       <c r="AH2">
-        <v>0.1086176026697414</v>
+        <v>0.09056204851118811</v>
       </c>
       <c r="AI2">
-        <v>0.05144815888676255</v>
+        <v>0.03815934371868001</v>
       </c>
       <c r="AJ2">
-        <v>9.793230996855934</v>
+        <v>4.126861527588471</v>
       </c>
       <c r="AK2">
-        <v>-0.983086720011882</v>
+        <v>-1.108897057826128</v>
       </c>
       <c r="AL2">
-        <v>1.044</v>
+        <v>0.425</v>
       </c>
       <c r="AM2">
-        <v>1.044</v>
+        <v>0.361</v>
       </c>
       <c r="AN2">
-        <v>-1.383522388059701</v>
+        <v>0.6283618581907091</v>
       </c>
       <c r="AO2">
-        <v>-10.95114942528736</v>
+        <v>17.07529411764706</v>
       </c>
       <c r="AP2">
-        <v>12.64525373134328</v>
+        <v>-8.328137734311328</v>
       </c>
       <c r="AQ2">
-        <v>-10.95114942528736</v>
+        <v>20.10249307479224</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Universal Insurance Plc (NGSE:UNIVINSURE)</t>
+          <t>Cornerstone Insurance Plc (NGSE:CORNERST)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,73 +722,76 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.393</v>
+        <v>0.13</v>
       </c>
       <c r="G3">
-        <v>0.3898704358068316</v>
+        <v>0.2013559322033898</v>
       </c>
       <c r="H3">
-        <v>0.3898704358068316</v>
+        <v>0.2013559322033898</v>
       </c>
       <c r="I3">
-        <v>0.3109540636042403</v>
+        <v>0.1715254237288135</v>
       </c>
       <c r="J3">
-        <v>0.3027648153642813</v>
+        <v>0.1633178965184889</v>
       </c>
       <c r="K3">
-        <v>2.55</v>
+        <v>6.8</v>
       </c>
       <c r="L3">
-        <v>0.3003533568904593</v>
+        <v>0.2305084745762712</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.12</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.08760330578512397</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3117647058823529</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.08677685950413223</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3088235294117647</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="T3">
+        <v>0.009433962264150952</v>
       </c>
       <c r="U3">
-        <v>0.8110000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="V3">
-        <v>0.1046451612903226</v>
+        <v>1.041322314049587</v>
       </c>
       <c r="W3">
-        <v>0.111353711790393</v>
+        <v>0.1531531531531531</v>
       </c>
       <c r="X3">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="Y3">
-        <v>0.02846497931995962</v>
+        <v>0.009507207577517218</v>
       </c>
       <c r="Z3">
-        <v>0.3863657049240011</v>
+        <v>2.5</v>
       </c>
       <c r="AA3">
-        <v>0.1169779413144056</v>
+        <v>0.4082947412962223</v>
       </c>
       <c r="AB3">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="AC3">
-        <v>0.03408920884397218</v>
+        <v>0.2646487957205864</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.8110000000000001</v>
+        <v>-25.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1168756304943075</v>
+        <v>25.2</v>
       </c>
       <c r="AK3">
-        <v>-0.03705057334734342</v>
+        <v>-1.150684931506849</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.3131274131274132</v>
+        <v>-4.565217391304348</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cornerstone Insurance Plc (NGSE:CORNERST)</t>
+          <t>Mutual Benefits Assurance Plc (NGSE:MBENEFIT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,37 +847,34 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.234</v>
-      </c>
-      <c r="E4">
-        <v>0.389</v>
+        <v>0.149</v>
       </c>
       <c r="G4">
-        <v>0.04448669201520912</v>
+        <v>-0.1466480446927374</v>
       </c>
       <c r="H4">
-        <v>0.04448669201520912</v>
+        <v>-0.1466480446927374</v>
       </c>
       <c r="I4">
-        <v>0.02524714828897338</v>
+        <v>0.07053072625698324</v>
       </c>
       <c r="J4">
-        <v>0.02524714828897338</v>
+        <v>0.06507907591827922</v>
       </c>
       <c r="K4">
-        <v>6.81</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
-        <v>0.25893536121673</v>
+        <v>0.04888268156424581</v>
       </c>
       <c r="M4">
-        <v>0.025</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.001243781094527363</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.003671071953010279</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,73 +886,73 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.025</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>32.6</v>
+        <v>38.7</v>
       </c>
       <c r="V4">
-        <v>1.621890547263682</v>
+        <v>3.198347107438017</v>
       </c>
       <c r="W4">
-        <v>0.1606132075471698</v>
+        <v>0.06986027944111776</v>
       </c>
       <c r="X4">
-        <v>0.08288873247043339</v>
+        <v>0.149274699810837</v>
       </c>
       <c r="Y4">
-        <v>0.07772447507673642</v>
+        <v>-0.07941442036971925</v>
       </c>
       <c r="Z4">
-        <v>2.858695652173914</v>
+        <v>2.700867597133157</v>
       </c>
       <c r="AA4">
-        <v>0.0721739130434783</v>
+        <v>0.1757699673990491</v>
       </c>
       <c r="AB4">
-        <v>0.08288873247043339</v>
+        <v>0.1455388460003668</v>
       </c>
       <c r="AC4">
-        <v>-0.0107148194269551</v>
+        <v>0.03023112139868228</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.928</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.928</v>
       </c>
       <c r="AG4">
-        <v>-32.6</v>
+        <v>-37.77200000000001</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.07123119435062941</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.01701877934272301</v>
       </c>
       <c r="AJ4">
-        <v>2.608</v>
+        <v>1.471330632595824</v>
       </c>
       <c r="AK4">
-        <v>-2.608</v>
+        <v>-2.386403841293911</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.1608318890814558</v>
       </c>
       <c r="AP4">
-        <v>-28.8495575221239</v>
+        <v>-6.546273830155981</v>
+      </c>
+      <c r="AQ4">
+        <v>-78.90625</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coronation Insurance Plc (NGSE:WAPIC)</t>
+          <t>Universal Insurance Plc (NGSE:UNIVINSURE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.102</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="G5">
-        <v>0.02297491039426524</v>
+        <v>0.1251282051282051</v>
       </c>
       <c r="H5">
-        <v>0.02297491039426524</v>
+        <v>0.1251282051282051</v>
       </c>
       <c r="I5">
-        <v>-0.1211469534050179</v>
+        <v>0.1815384615384615</v>
       </c>
       <c r="J5">
-        <v>-0.1211469534050179</v>
+        <v>0.1792431476569408</v>
       </c>
       <c r="K5">
-        <v>-1.22</v>
+        <v>1.72</v>
       </c>
       <c r="L5">
-        <v>-0.04372759856630824</v>
+        <v>0.1764102564102564</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1008,79 +1008,73 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>21.8</v>
+        <v>1.51</v>
       </c>
       <c r="V5">
-        <v>0.6687116564417178</v>
+        <v>0.211484593837535</v>
       </c>
       <c r="W5">
-        <v>-0.01912225705329154</v>
+        <v>0.07577092511013216</v>
       </c>
       <c r="X5">
-        <v>0.08326281814440367</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="Y5">
-        <v>-0.1023850751976952</v>
+        <v>-0.06787502046550377</v>
       </c>
       <c r="Z5">
-        <v>0.490454593397321</v>
+        <v>0.4454292110192334</v>
       </c>
       <c r="AA5">
-        <v>-0.05941707977358227</v>
+        <v>0.07984013384143508</v>
       </c>
       <c r="AB5">
-        <v>0.08302103960633665</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="AC5">
-        <v>-0.1424381193799189</v>
+        <v>-0.06380581173420084</v>
       </c>
       <c r="AD5">
-        <v>0.257</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.257</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-21.543</v>
+        <v>-1.51</v>
       </c>
       <c r="AH5">
-        <v>0.007821773138144078</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.004552137024638221</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-1.948358505923849</v>
+        <v>-0.2682060390763766</v>
       </c>
       <c r="AK5">
-        <v>-0.6216060247569033</v>
+        <v>-0.07126002831524304</v>
       </c>
       <c r="AL5">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>-0.1084388185654008</v>
-      </c>
-      <c r="AO5">
-        <v>-46.3013698630137</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>9.089873417721519</v>
-      </c>
-      <c r="AQ5">
-        <v>-46.3013698630137</v>
+        <v>-0.6990740740740741</v>
       </c>
     </row>
     <row r="6">
@@ -1100,25 +1094,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0254</v>
+        <v>0.0436</v>
       </c>
       <c r="G6">
-        <v>-0.2364406779661017</v>
+        <v>-0.03595505617977528</v>
       </c>
       <c r="H6">
-        <v>-0.2364406779661017</v>
+        <v>-0.03595505617977528</v>
       </c>
       <c r="I6">
-        <v>-0.111864406779661</v>
+        <v>-0.2108614232209738</v>
       </c>
       <c r="J6">
-        <v>-0.111864406779661</v>
+        <v>-0.2108614232209738</v>
       </c>
       <c r="K6">
-        <v>-0.194</v>
+        <v>-0.331</v>
       </c>
       <c r="L6">
-        <v>-0.08220338983050848</v>
+        <v>-0.1239700374531835</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1142,31 +1136,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.14</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="V6">
-        <v>0.3825503355704697</v>
+        <v>0.3419708029197081</v>
       </c>
       <c r="W6">
-        <v>-0.03559633027522936</v>
+        <v>-0.06389961389961391</v>
       </c>
       <c r="X6">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="Y6">
-        <v>-0.1184850627456628</v>
+        <v>-0.2075455594752498</v>
       </c>
       <c r="Z6">
-        <v>0.5914786967418546</v>
+        <v>0.6608910891089109</v>
       </c>
       <c r="AA6">
-        <v>-0.06616541353383458</v>
+        <v>-0.1393564356435643</v>
       </c>
       <c r="AB6">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="AC6">
-        <v>-0.149054146004268</v>
+        <v>-0.2830023812192003</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1178,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-1.14</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1187,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.6195652173913042</v>
+        <v>-0.5196894065446478</v>
       </c>
       <c r="AK6">
-        <v>-0.2821782178217822</v>
+        <v>-0.2530380772346746</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1202,7 +1196,7 @@
         <v>-0</v>
       </c>
       <c r="AP6">
-        <v>7.124999999999999</v>
+        <v>2.764011799410029</v>
       </c>
     </row>
     <row r="7">
@@ -1225,76 +1219,73 @@
         <v>0.214</v>
       </c>
       <c r="E7">
-        <v>-0.0211</v>
+        <v>-0.332</v>
       </c>
       <c r="G7">
-        <v>0.001275720164609054</v>
+        <v>-0.01721311475409836</v>
       </c>
       <c r="H7">
-        <v>0.001275720164609054</v>
+        <v>-0.01721311475409836</v>
       </c>
       <c r="I7">
-        <v>-0.0408641975308642</v>
+        <v>-0.07049180327868852</v>
       </c>
       <c r="J7">
-        <v>-0.0408641975308642</v>
+        <v>-0.03524590163934426</v>
       </c>
       <c r="K7">
-        <v>0.832</v>
+        <v>0.193</v>
       </c>
       <c r="L7">
-        <v>0.03423868312757201</v>
+        <v>0.00790983606557377</v>
       </c>
       <c r="M7">
-        <v>0.893</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.1916309012875536</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.073317307692308</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>0.893</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1916309012875536</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.073317307692308</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>24.7</v>
+        <v>20.2</v>
       </c>
       <c r="V7">
-        <v>5.300429184549356</v>
+        <v>5.674157303370786</v>
       </c>
       <c r="W7">
-        <v>0.03665198237885463</v>
+        <v>0.007043795620437956</v>
       </c>
       <c r="X7">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="Y7">
-        <v>-0.04623675009157877</v>
+        <v>-0.136602149955198</v>
       </c>
       <c r="Z7">
-        <v>3.24</v>
+        <v>9.037037037037038</v>
       </c>
       <c r="AA7">
-        <v>-0.1324</v>
+        <v>-0.3185185185185186</v>
       </c>
       <c r="AB7">
-        <v>0.08288873247043339</v>
+        <v>0.1436459455756359</v>
       </c>
       <c r="AC7">
-        <v>-0.2152887324704334</v>
+        <v>-0.4621644640941545</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1306,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-24.7</v>
+        <v>-20.2</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1315,28 +1306,28 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>1.232534930139721</v>
+        <v>1.213942307692308</v>
       </c>
       <c r="AK7">
-        <v>-9.148148148148151</v>
+        <v>-3.06060606060606</v>
       </c>
       <c r="AL7">
-        <v>0.025</v>
+        <v>0.122</v>
       </c>
       <c r="AM7">
-        <v>0.025</v>
+        <v>0.122</v>
       </c>
       <c r="AN7">
         <v>-0</v>
       </c>
       <c r="AO7">
-        <v>-39.72</v>
+        <v>-14.09836065573771</v>
       </c>
       <c r="AP7">
-        <v>62.53164556962025</v>
+        <v>20.30150753768844</v>
       </c>
       <c r="AQ7">
-        <v>-39.72</v>
+        <v>-14.09836065573771</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mutual Benefits Assurance Plc (NGSE:MBENEFIT)</t>
+          <t>Royal Exchange Plc (NGSE:ROYALEX)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,243 +1347,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08929999999999999</v>
+        <v>-0.38</v>
       </c>
       <c r="G8">
-        <v>0.2231578947368421</v>
+        <v>-0.2872340425531915</v>
       </c>
       <c r="H8">
-        <v>0.2231578947368421</v>
+        <v>-0.2872340425531915</v>
       </c>
       <c r="I8">
-        <v>-0.1749473684210526</v>
+        <v>-0.9957446808510637</v>
       </c>
       <c r="J8">
-        <v>-0.1749473684210526</v>
+        <v>-0.9957446808510637</v>
       </c>
       <c r="K8">
-        <v>-2.05</v>
+        <v>-2.22</v>
       </c>
       <c r="L8">
-        <v>-0.0431578947368421</v>
+        <v>-0.9446808510638298</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.025</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.002049180327868853</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0.01126126126126126</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.025</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.002049180327868853</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0.01126126126126126</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>29.1</v>
+        <v>1.37</v>
       </c>
       <c r="V8">
-        <v>1.81875</v>
+        <v>0.1122950819672131</v>
       </c>
       <c r="W8">
-        <v>-0.04371002132196162</v>
+        <v>-0.7278688524590164</v>
       </c>
       <c r="X8">
-        <v>0.09923005379158724</v>
+        <v>0.1751684806880484</v>
       </c>
       <c r="Y8">
-        <v>-0.1429400751135489</v>
+        <v>-0.9030373331470649</v>
       </c>
       <c r="Z8">
-        <v>1.392961876832845</v>
+        <v>1.5359477124183</v>
       </c>
       <c r="AA8">
-        <v>-0.2436950146627566</v>
+        <v>-1.529411764705881</v>
       </c>
       <c r="AB8">
-        <v>0.0877680516778159</v>
+        <v>0.1516303467295297</v>
       </c>
       <c r="AC8">
-        <v>-0.3314630663405725</v>
+        <v>-1.681042111435411</v>
       </c>
       <c r="AD8">
-        <v>5.51</v>
+        <v>5.24</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>5.51</v>
+        <v>5.24</v>
       </c>
       <c r="AG8">
-        <v>-23.59</v>
+        <v>3.87</v>
       </c>
       <c r="AH8">
-        <v>0.2561599256159926</v>
+        <v>0.3004587155963303</v>
       </c>
       <c r="AI8">
-        <v>0.09258948075953621</v>
+        <v>0.8926746166950597</v>
       </c>
       <c r="AJ8">
-        <v>3.108036890645586</v>
+        <v>0.2408214063472309</v>
       </c>
       <c r="AK8">
-        <v>-0.7757316672147322</v>
+        <v>0.86</v>
       </c>
       <c r="AL8">
-        <v>0.317</v>
+        <v>0.303</v>
       </c>
       <c r="AM8">
-        <v>0.317</v>
+        <v>0.303</v>
       </c>
       <c r="AN8">
-        <v>-0.7356475300400533</v>
+        <v>-2.278260869565218</v>
       </c>
       <c r="AO8">
-        <v>-26.21451104100947</v>
+        <v>-7.722772277227723</v>
       </c>
       <c r="AP8">
-        <v>3.149532710280374</v>
+        <v>-1.682608695652174</v>
       </c>
       <c r="AQ8">
-        <v>-26.21451104100947</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Royal Exchange Plc (NGSE:ROYALEX)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.165</v>
-      </c>
-      <c r="G9">
-        <v>0.2870466321243523</v>
-      </c>
-      <c r="H9">
-        <v>0.2870466321243523</v>
-      </c>
-      <c r="I9">
-        <v>-0.1854922279792746</v>
-      </c>
-      <c r="J9">
-        <v>-0.1854922279792746</v>
-      </c>
-      <c r="K9">
-        <v>-2.53</v>
-      </c>
-      <c r="L9">
-        <v>-0.2621761658031088</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>7.34</v>
-      </c>
-      <c r="V9">
-        <v>0.6672727272727272</v>
-      </c>
-      <c r="W9">
-        <v>-0.2238938053097345</v>
-      </c>
-      <c r="X9">
-        <v>0.1079952139326648</v>
-      </c>
-      <c r="Y9">
-        <v>-0.3318890192423993</v>
-      </c>
-      <c r="Z9">
-        <v>3.092948717948719</v>
-      </c>
-      <c r="AA9">
-        <v>-0.5737179487179489</v>
-      </c>
-      <c r="AB9">
-        <v>0.0894796372225503</v>
-      </c>
-      <c r="AC9">
-        <v>-0.6631975859404992</v>
-      </c>
-      <c r="AD9">
-        <v>5.82</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>5.82</v>
-      </c>
-      <c r="AG9">
-        <v>-1.52</v>
-      </c>
-      <c r="AH9">
-        <v>0.3460166468489893</v>
-      </c>
-      <c r="AI9">
-        <v>0.6561443066516347</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.160337552742616</v>
-      </c>
-      <c r="AK9">
-        <v>-0.9934640522875813</v>
-      </c>
-      <c r="AL9">
-        <v>0.629</v>
-      </c>
-      <c r="AM9">
-        <v>0.629</v>
-      </c>
-      <c r="AN9">
-        <v>-3.464285714285714</v>
-      </c>
-      <c r="AO9">
-        <v>-2.845786963434022</v>
-      </c>
-      <c r="AP9">
-        <v>0.9047619047619045</v>
-      </c>
-      <c r="AQ9">
-        <v>-2.845786963434022</v>
+        <v>-7.722772277227723</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1395</v>
+        <v>0.165</v>
       </c>
       <c r="E2">
-        <v>-0.332</v>
+        <v>-0.00387</v>
       </c>
       <c r="G2">
-        <v>-0.03230198902117346</v>
+        <v>0.2221486651795352</v>
       </c>
       <c r="H2">
-        <v>-0.03230198902117346</v>
+        <v>0.2221486651795352</v>
       </c>
       <c r="I2">
-        <v>0.05173593783417695</v>
+        <v>0.1434842052241491</v>
       </c>
       <c r="J2">
-        <v>0.04623650618043326</v>
+        <v>0.1329024295696901</v>
       </c>
       <c r="K2">
-        <v>9.661999999999999</v>
+        <v>29.588</v>
       </c>
       <c r="L2">
-        <v>0.06888144293148928</v>
+        <v>0.2129092609915809</v>
       </c>
       <c r="M2">
-        <v>2.145</v>
+        <v>1.752</v>
       </c>
       <c r="N2">
-        <v>0.03463028737487892</v>
+        <v>0.02379141770776751</v>
       </c>
       <c r="O2">
-        <v>0.2220037259366591</v>
+        <v>0.05921319453832635</v>
       </c>
       <c r="P2">
-        <v>2.125</v>
+        <v>1.752</v>
       </c>
       <c r="Q2">
-        <v>0.03430739425250242</v>
+        <v>0.02379141770776751</v>
       </c>
       <c r="R2">
-        <v>0.2199337611260609</v>
+        <v>0.05921319453832635</v>
       </c>
       <c r="S2">
-        <v>0.02000000000000002</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.009324009324009333</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>87.917</v>
+        <v>81.586</v>
       </c>
       <c r="V2">
-        <v>1.419389731998709</v>
+        <v>1.107903313416621</v>
       </c>
       <c r="W2">
-        <v>0.03845203753077786</v>
+        <v>0.1105367793240557</v>
       </c>
       <c r="X2">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="Y2">
-        <v>-0.1051939080448581</v>
+        <v>-0.02516209056123102</v>
       </c>
       <c r="Z2">
-        <v>2.048664359053002</v>
+        <v>1.997154518280065</v>
       </c>
       <c r="AA2">
-        <v>-0.02975815090106463</v>
+        <v>0.05387763894872901</v>
       </c>
       <c r="AB2">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="AC2">
-        <v>-0.1734040964767006</v>
+        <v>-0.08182123093655766</v>
       </c>
       <c r="AD2">
-        <v>6.168</v>
+        <v>3.098</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.168</v>
+        <v>3.098</v>
       </c>
       <c r="AG2">
-        <v>-81.749</v>
+        <v>-78.488</v>
       </c>
       <c r="AH2">
-        <v>0.09056204851118811</v>
+        <v>0.04037113294586776</v>
       </c>
       <c r="AI2">
-        <v>0.03815934371868001</v>
+        <v>0.02119623968581945</v>
       </c>
       <c r="AJ2">
-        <v>4.126861527588471</v>
+        <v>16.18976897689769</v>
       </c>
       <c r="AK2">
-        <v>-1.108897057826128</v>
+        <v>-1.215511367156043</v>
       </c>
       <c r="AL2">
-        <v>0.425</v>
+        <v>4.363</v>
       </c>
       <c r="AM2">
-        <v>0.361</v>
+        <v>4.363</v>
       </c>
       <c r="AN2">
-        <v>0.6283618581907091</v>
+        <v>0.1401556279406442</v>
       </c>
       <c r="AO2">
-        <v>17.07529411764706</v>
+        <v>4.570249828099932</v>
       </c>
       <c r="AP2">
-        <v>-8.328137734311328</v>
+        <v>-3.550850524791892</v>
       </c>
       <c r="AQ2">
-        <v>20.10249307479224</v>
+        <v>4.570249828099932</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cornerstone Insurance Plc (NGSE:CORNERST)</t>
+          <t>Coronation Insurance Plc (NGSE:WAPIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,100 +722,85 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.13</v>
+        <v>0.133</v>
+      </c>
+      <c r="E3">
+        <v>-0.0255</v>
       </c>
       <c r="G3">
-        <v>0.2013559322033898</v>
+        <v>0.2378223495702006</v>
       </c>
       <c r="H3">
-        <v>0.2013559322033898</v>
+        <v>0.2378223495702006</v>
       </c>
       <c r="I3">
-        <v>0.1715254237288135</v>
+        <v>0.2217765042979943</v>
       </c>
       <c r="J3">
-        <v>0.1633178965184889</v>
+        <v>0.1951112941038073</v>
       </c>
       <c r="K3">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>0.2305084745762712</v>
+        <v>0.08595988538681949</v>
       </c>
       <c r="M3">
-        <v>2.12</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08760330578512397</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3117647058823529</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08677685950413223</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3088235294117647</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="T3">
-        <v>0.009433962264150952</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>25.2</v>
+        <v>10.5</v>
       </c>
       <c r="V3">
-        <v>1.041322314049587</v>
-      </c>
-      <c r="W3">
-        <v>0.1531531531531531</v>
+        <v>0.5706521739130436</v>
       </c>
       <c r="X3">
-        <v>0.1436459455756359</v>
-      </c>
-      <c r="Y3">
-        <v>0.009507207577517218</v>
-      </c>
-      <c r="Z3">
-        <v>2.5</v>
-      </c>
-      <c r="AA3">
-        <v>0.4082947412962223</v>
+        <v>0.1358242064669861</v>
       </c>
       <c r="AB3">
-        <v>0.1436459455756359</v>
-      </c>
-      <c r="AC3">
-        <v>0.2646487957205864</v>
+        <v>0.1357482668833118</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AG3">
-        <v>-25.2</v>
+        <v>-10.466</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.001844417923402409</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.001248439450686642</v>
       </c>
       <c r="AJ3">
-        <v>25.2</v>
+        <v>-1.319132845979329</v>
       </c>
       <c r="AK3">
-        <v>-1.150684931506849</v>
+        <v>-0.6254332496713277</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.004096385542168675</v>
       </c>
       <c r="AP3">
-        <v>-4.565217391304348</v>
+        <v>-1.260963855421687</v>
       </c>
     </row>
     <row r="4">
@@ -847,25 +832,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.149</v>
+        <v>0.206</v>
+      </c>
+      <c r="E4">
+        <v>0.366</v>
       </c>
       <c r="G4">
-        <v>-0.1466480446927374</v>
+        <v>0.291746641074856</v>
       </c>
       <c r="H4">
-        <v>-0.1466480446927374</v>
+        <v>0.291746641074856</v>
       </c>
       <c r="I4">
-        <v>0.07053072625698324</v>
+        <v>0.1690978886756238</v>
       </c>
       <c r="J4">
-        <v>0.06507907591827922</v>
+        <v>0.1379420188915075</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>5.56</v>
       </c>
       <c r="L4">
-        <v>0.04888268156424581</v>
+        <v>0.1067178502879079</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,70 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>38.7</v>
+        <v>32.6</v>
       </c>
       <c r="V4">
-        <v>3.198347107438017</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="W4">
-        <v>0.06986027944111776</v>
+        <v>0.1105367793240557</v>
       </c>
       <c r="X4">
-        <v>0.149274699810837</v>
+        <v>0.1386042210006805</v>
       </c>
       <c r="Y4">
-        <v>-0.07941442036971925</v>
+        <v>-0.02806744167662485</v>
       </c>
       <c r="Z4">
-        <v>2.700867597133157</v>
+        <v>4.158684546615584</v>
       </c>
       <c r="AA4">
-        <v>0.1757699673990491</v>
+        <v>0.573657342293067</v>
       </c>
       <c r="AB4">
-        <v>0.1455388460003668</v>
+        <v>0.1367221706112019</v>
       </c>
       <c r="AC4">
-        <v>0.03023112139868228</v>
+        <v>0.436935171681865</v>
       </c>
       <c r="AD4">
-        <v>0.928</v>
+        <v>0.514</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.928</v>
+        <v>0.514</v>
       </c>
       <c r="AG4">
-        <v>-37.77200000000001</v>
+        <v>-32.086</v>
       </c>
       <c r="AH4">
-        <v>0.07123119435062941</v>
+        <v>0.041073997123222</v>
       </c>
       <c r="AI4">
-        <v>0.01701877934272301</v>
+        <v>0.01338053834539491</v>
       </c>
       <c r="AJ4">
-        <v>1.471330632595824</v>
+        <v>1.59743104650005</v>
       </c>
       <c r="AK4">
-        <v>-2.386403841293911</v>
+        <v>-5.518747850017199</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AM4">
-        <v>-0.064</v>
+        <v>3.84</v>
       </c>
       <c r="AN4">
-        <v>0.1608318890814558</v>
+        <v>0.05617486338797814</v>
+      </c>
+      <c r="AO4">
+        <v>2.294270833333333</v>
       </c>
       <c r="AP4">
-        <v>-6.546273830155981</v>
+        <v>-3.506666666666666</v>
       </c>
       <c r="AQ4">
-        <v>-78.90625</v>
+        <v>2.294270833333333</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Universal Insurance Plc (NGSE:UNIVINSURE)</t>
+          <t>Royal Exchange Plc (NGSE:ROYALEX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,25 +963,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.3779999999999999</v>
+        <v>-0.287</v>
       </c>
       <c r="G5">
-        <v>0.1251282051282051</v>
+        <v>0.144140625</v>
       </c>
       <c r="H5">
-        <v>0.1251282051282051</v>
+        <v>0.144140625</v>
       </c>
       <c r="I5">
-        <v>0.1815384615384615</v>
+        <v>0.7890625</v>
       </c>
       <c r="J5">
-        <v>0.1792431476569408</v>
+        <v>0.7806082589285714</v>
       </c>
       <c r="K5">
-        <v>1.72</v>
+        <v>1.21</v>
       </c>
       <c r="L5">
-        <v>0.1764102564102564</v>
+        <v>0.47265625</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,67 +1005,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.51</v>
+        <v>0.909</v>
       </c>
       <c r="V5">
-        <v>0.211484593837535</v>
+        <v>0.249041095890411</v>
       </c>
       <c r="W5">
-        <v>0.07577092511013216</v>
+        <v>1.92063492063492</v>
       </c>
       <c r="X5">
-        <v>0.1436459455756359</v>
+        <v>0.1830863994045296</v>
       </c>
       <c r="Y5">
-        <v>-0.06787502046550377</v>
+        <v>1.737548521230391</v>
       </c>
       <c r="Z5">
-        <v>0.4454292110192334</v>
+        <v>0.5688888888888889</v>
       </c>
       <c r="AA5">
-        <v>0.07984013384143508</v>
+        <v>0.4440793650793651</v>
       </c>
       <c r="AB5">
-        <v>0.1436459455756359</v>
+        <v>0.1467140020819932</v>
       </c>
       <c r="AC5">
-        <v>-0.06380581173420084</v>
+        <v>0.2973653629973719</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG5">
-        <v>-1.51</v>
+        <v>1.641</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.4112903225806452</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.4569892473118279</v>
       </c>
       <c r="AJ5">
-        <v>-0.2682060390763766</v>
+        <v>0.3101493101493101</v>
       </c>
       <c r="AK5">
-        <v>-0.07126002831524304</v>
+        <v>0.3513166345536288</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.262376237623762</v>
+      </c>
+      <c r="AO5">
+        <v>4.580498866213152</v>
       </c>
       <c r="AP5">
-        <v>-0.6990740740740741</v>
+        <v>0.8123762376237623</v>
+      </c>
+      <c r="AQ5">
+        <v>4.580498866213152</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Guinea Insurance Plc (NGSE:GUINEAINS)</t>
+          <t>Cornerstone Insurance Plc (NGSE:CORNERST)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,73 +1091,76 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0436</v>
+        <v>0.165</v>
       </c>
       <c r="G6">
-        <v>-0.03595505617977528</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="H6">
-        <v>-0.03595505617977528</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="I6">
-        <v>-0.2108614232209738</v>
+        <v>0.05648148148148148</v>
       </c>
       <c r="J6">
-        <v>-0.2108614232209738</v>
+        <v>0.05263047138047138</v>
       </c>
       <c r="K6">
-        <v>-0.331</v>
+        <v>16.2</v>
       </c>
       <c r="L6">
-        <v>-0.1239700374531835</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.4</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04929577464788732</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.08641975308641975</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04929577464788732</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.08641975308641975</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.9370000000000001</v>
+        <v>21.7</v>
       </c>
       <c r="V6">
-        <v>0.3419708029197081</v>
+        <v>0.7640845070422535</v>
       </c>
       <c r="W6">
-        <v>-0.06389961389961391</v>
+        <v>0.3498920086393089</v>
       </c>
       <c r="X6">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="Y6">
-        <v>-0.2075455594752498</v>
+        <v>0.2141931387540222</v>
       </c>
       <c r="Z6">
-        <v>0.6608910891089109</v>
+        <v>1.023696682464455</v>
       </c>
       <c r="AA6">
-        <v>-0.1393564356435643</v>
+        <v>0.05387763894872901</v>
       </c>
       <c r="AB6">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="AC6">
-        <v>-0.2830023812192003</v>
+        <v>-0.08182123093655766</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.9370000000000001</v>
+        <v>-21.7</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1181,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.5196894065446478</v>
+        <v>-3.238805970149254</v>
       </c>
       <c r="AK6">
-        <v>-0.2530380772346746</v>
+        <v>-1.090452261306533</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1193,10 +1193,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.764011799410029</v>
+        <v>-14.18300653594771</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LASACO Assurance Plc (NGSE:LASACO)</t>
+          <t>Universal Insurance Plc (NGSE:UNIVINSURE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,28 +1216,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.214</v>
+        <v>0.5</v>
       </c>
       <c r="E7">
-        <v>-0.332</v>
+        <v>-0.00387</v>
       </c>
       <c r="G7">
-        <v>-0.01721311475409836</v>
+        <v>0.1848184818481848</v>
       </c>
       <c r="H7">
-        <v>-0.01721311475409836</v>
+        <v>0.1848184818481848</v>
       </c>
       <c r="I7">
-        <v>-0.07049180327868852</v>
+        <v>0.1276127612761276</v>
       </c>
       <c r="J7">
-        <v>-0.03524590163934426</v>
+        <v>0.1239517394362387</v>
       </c>
       <c r="K7">
-        <v>0.193</v>
+        <v>1.19</v>
       </c>
       <c r="L7">
-        <v>0.00790983606557377</v>
+        <v>0.1309130913091309</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1261,31 +1261,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>20.2</v>
+        <v>1.68</v>
       </c>
       <c r="V7">
-        <v>5.674157303370786</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="W7">
-        <v>0.007043795620437956</v>
+        <v>0.05242290748898679</v>
       </c>
       <c r="X7">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="Y7">
-        <v>-0.136602149955198</v>
+        <v>-0.08327596239629989</v>
       </c>
       <c r="Z7">
-        <v>9.037037037037038</v>
+        <v>0.4289759320434167</v>
       </c>
       <c r="AA7">
-        <v>-0.3185185185185186</v>
+        <v>0.05317231295306323</v>
       </c>
       <c r="AB7">
-        <v>0.1436459455756359</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="AC7">
-        <v>-0.4621644640941545</v>
+        <v>-0.08252655693222344</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-20.2</v>
+        <v>-1.68</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1306,28 +1306,22 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>1.213942307692308</v>
+        <v>-0.5599999999999999</v>
       </c>
       <c r="AK7">
-        <v>-3.06060606060606</v>
+        <v>-0.1386138613861386</v>
       </c>
       <c r="AL7">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AO7">
-        <v>-14.09836065573771</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>20.30150753768844</v>
-      </c>
-      <c r="AQ7">
-        <v>-14.09836065573771</v>
+        <v>-1.217391304347826</v>
       </c>
     </row>
     <row r="8">
@@ -1338,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Royal Exchange Plc (NGSE:ROYALEX)</t>
+          <t>Guinea Insurance Plc (NGSE:GUINEAINS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1347,118 +1341,246 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.38</v>
+        <v>0.0767</v>
+      </c>
+      <c r="E8">
+        <v>-0.0458</v>
       </c>
       <c r="G8">
-        <v>-0.2872340425531915</v>
+        <v>-0.1088541666666667</v>
       </c>
       <c r="H8">
-        <v>-0.2872340425531915</v>
+        <v>-0.1088541666666667</v>
       </c>
       <c r="I8">
-        <v>-0.9957446808510637</v>
+        <v>-0.0078125</v>
       </c>
       <c r="J8">
-        <v>-0.9957446808510637</v>
+        <v>-0.007092927631578948</v>
       </c>
       <c r="K8">
-        <v>-2.22</v>
+        <v>0.138</v>
       </c>
       <c r="L8">
-        <v>-0.9446808510638298</v>
+        <v>0.07187500000000001</v>
       </c>
       <c r="M8">
-        <v>0.025</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.002049180327868853</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.01126126126126126</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.025</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.002049180327868853</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0.01126126126126126</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>1.37</v>
+        <v>0.797</v>
       </c>
       <c r="V8">
-        <v>0.1122950819672131</v>
+        <v>0.3077220077220078</v>
       </c>
       <c r="W8">
-        <v>-0.7278688524590164</v>
+        <v>0.02974137931034483</v>
       </c>
       <c r="X8">
-        <v>0.1751684806880484</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="Y8">
-        <v>-0.9030373331470649</v>
+        <v>-0.1059574905749418</v>
       </c>
       <c r="Z8">
-        <v>1.5359477124183</v>
+        <v>0.5237315875613748</v>
       </c>
       <c r="AA8">
-        <v>-1.529411764705881</v>
+        <v>-0.003714790248944785</v>
       </c>
       <c r="AB8">
-        <v>0.1516303467295297</v>
+        <v>0.1356988698852867</v>
       </c>
       <c r="AC8">
-        <v>-1.681042111435411</v>
+        <v>-0.1394136601342315</v>
       </c>
       <c r="AD8">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>3.87</v>
+        <v>-0.797</v>
       </c>
       <c r="AH8">
-        <v>0.3004587155963303</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.8926746166950597</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.2408214063472309</v>
+        <v>-0.4445064138315673</v>
       </c>
       <c r="AK8">
-        <v>0.86</v>
+        <v>-0.4598961338718985</v>
       </c>
       <c r="AL8">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>-2.278260869565218</v>
-      </c>
-      <c r="AO8">
-        <v>-7.722772277227723</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-1.682608695652174</v>
-      </c>
-      <c r="AQ8">
-        <v>-7.722772277227723</v>
+        <v>-7.97</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LASACO Assurance Plc (NGSE:LASACO)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.21</v>
+      </c>
+      <c r="E9">
+        <v>0.174</v>
+      </c>
+      <c r="G9">
+        <v>0.02214285714285714</v>
+      </c>
+      <c r="H9">
+        <v>0.02214285714285714</v>
+      </c>
+      <c r="I9">
+        <v>-0.05922619047619047</v>
+      </c>
+      <c r="J9">
+        <v>-0.05851139162561576</v>
+      </c>
+      <c r="K9">
+        <v>2.29</v>
+      </c>
+      <c r="L9">
+        <v>0.1363095238095238</v>
+      </c>
+      <c r="M9">
+        <v>0.352</v>
+      </c>
+      <c r="N9">
+        <v>0.08979591836734693</v>
+      </c>
+      <c r="O9">
+        <v>0.1537117903930131</v>
+      </c>
+      <c r="P9">
+        <v>0.352</v>
+      </c>
+      <c r="Q9">
+        <v>0.08979591836734693</v>
+      </c>
+      <c r="R9">
+        <v>0.1537117903930131</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>13.4</v>
+      </c>
+      <c r="V9">
+        <v>3.418367346938776</v>
+      </c>
+      <c r="W9">
+        <v>0.08544776119402984</v>
+      </c>
+      <c r="X9">
+        <v>0.1356988698852867</v>
+      </c>
+      <c r="Y9">
+        <v>-0.05025110869125683</v>
+      </c>
+      <c r="Z9">
+        <v>2.545454545454545</v>
+      </c>
+      <c r="AA9">
+        <v>-0.1489380877742947</v>
+      </c>
+      <c r="AB9">
+        <v>0.1356988698852867</v>
+      </c>
+      <c r="AC9">
+        <v>-0.2846369576595813</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>-13.4</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>1.413502109704641</v>
+      </c>
+      <c r="AK9">
+        <v>-3.722222222222223</v>
+      </c>
+      <c r="AL9">
+        <v>0.082</v>
+      </c>
+      <c r="AM9">
+        <v>0.082</v>
+      </c>
+      <c r="AN9">
+        <v>-0</v>
+      </c>
+      <c r="AO9">
+        <v>-12.13414634146341</v>
+      </c>
+      <c r="AP9">
+        <v>35.63829787234042</v>
+      </c>
+      <c r="AQ9">
+        <v>-12.13414634146341</v>
       </c>
     </row>
   </sheetData>
